--- a/results/exp09-c100-resnet-e32-k12-posthoc/20260925-043635/rounds.xlsx
+++ b/results/exp09-c100-resnet-e32-k12-posthoc/20260925-043635/rounds.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U43"/>
+  <dimension ref="A1:U101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4021,6 +4021,4820 @@
         </is>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2026-09-25 05:24:50</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E44" t="n">
+        <v>1.665147655305804</v>
+      </c>
+      <c r="F44" t="n">
+        <v>54.19</v>
+      </c>
+      <c r="G44" t="n">
+        <v>55.14</v>
+      </c>
+      <c r="H44" t="n">
+        <v>42</v>
+      </c>
+      <c r="I44" t="n">
+        <v>68.6566</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>1:08.66</t>
+        </is>
+      </c>
+      <c r="K44" t="n">
+        <v>67.1985</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0.1634</v>
+      </c>
+      <c r="M44" t="n">
+        <v>1.2893</v>
+      </c>
+      <c r="N44" t="n">
+        <v>2894.7043</v>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>48:14.70</t>
+        </is>
+      </c>
+      <c r="P44" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>5,1,2,8,9,7,4,6,3,0</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>5:18;1:19;2:17;8:15;9:11;7:10;4:11;6:10;3:20;0:10</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>5:[16];1:[13];2:[14];8:[13];9:[14];7:[15];4:[14];6:[14];3:[16,17];0:[14]</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>c5:bw=18,experts=[16]; c1:bw=19,experts=[13]; c2:bw=17,experts=[14]; c8:bw=15,experts=[13]; c9:bw=11,experts=[14]; c7:bw=10,experts=[15]; c4:bw=11,experts=[14]; c6:bw=10,experts=[14]; c3:bw=20,experts=[16,17]; c0:bw=10,experts=[14]</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>8.2338,5.6309,5.0280,7.0035,4.6639,6.1618,8.8508,8.8562,6.6946,6.0750</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2026-09-25 05:25:58</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E45" t="n">
+        <v>1.663150861235687</v>
+      </c>
+      <c r="F45" t="n">
+        <v>54.58</v>
+      </c>
+      <c r="G45" t="n">
+        <v>55.14</v>
+      </c>
+      <c r="H45" t="n">
+        <v>42</v>
+      </c>
+      <c r="I45" t="n">
+        <v>68.413</v>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>1:08.41</t>
+        </is>
+      </c>
+      <c r="K45" t="n">
+        <v>66.9477</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0.1678</v>
+      </c>
+      <c r="M45" t="n">
+        <v>1.296</v>
+      </c>
+      <c r="N45" t="n">
+        <v>2963.141</v>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>49:23.14</t>
+        </is>
+      </c>
+      <c r="P45" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>0,3,4,2,7,5,6,9,8,1</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>0:20;3:16;4:10;2:12;7:20;5:10;6:10;9:12;8:11;1:15</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>0:[15,16];3:[18];4:[15];2:[15];7:[16,17];5:[17];6:[15];9:[15];8:[14];1:[14]</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>c0:bw=20,experts=[15,16]; c3:bw=16,experts=[18]; c4:bw=10,experts=[15]; c2:bw=12,experts=[15]; c7:bw=20,experts=[16,17]; c5:bw=10,experts=[17]; c6:bw=10,experts=[15]; c9:bw=12,experts=[15]; c8:bw=11,experts=[14]; c1:bw=15,experts=[14]</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>5.9421,6.4983,8.7195,5.0022,6.2256,8.4326,9.0265,4.6779,6.8698,5.5532</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2026-09-25 05:27:07</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E46" t="n">
+        <v>1.651035014865521</v>
+      </c>
+      <c r="F46" t="n">
+        <v>55.19</v>
+      </c>
+      <c r="G46" t="n">
+        <v>55.19</v>
+      </c>
+      <c r="H46" t="n">
+        <v>45</v>
+      </c>
+      <c r="I46" t="n">
+        <v>68.4973</v>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>1:08.50</t>
+        </is>
+      </c>
+      <c r="K46" t="n">
+        <v>66.9659</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0.1725</v>
+      </c>
+      <c r="M46" t="n">
+        <v>1.3575</v>
+      </c>
+      <c r="N46" t="n">
+        <v>3031.6652</v>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>50:31.67</t>
+        </is>
+      </c>
+      <c r="P46" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>8,0,3,4,7,2,9,6,5,1</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>8:18;0:12;3:20;4:20;7:12;2:16;9:10;6:10;5:15;1:19</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>8:[15];0:[17];3:[19,20];4:[16,17];7:[18];2:[16];9:[16];6:[16];5:[18];1:[15]</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>c8:bw=18,experts=[15]; c0:bw=12,experts=[17]; c3:bw=20,experts=[19,20]; c4:bw=20,experts=[16,17]; c7:bw=12,experts=[18]; c2:bw=16,experts=[16]; c9:bw=10,experts=[16]; c6:bw=10,experts=[16]; c5:bw=15,experts=[18]; c1:bw=19,experts=[15]</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>6.9427,6.1697,6.7005,8.7447,5.9715,5.0390,4.6256,8.7564,8.2030,5.8127</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2026-09-25 05:28:15</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E47" t="n">
+        <v>1.644018921999244</v>
+      </c>
+      <c r="F47" t="n">
+        <v>56.08</v>
+      </c>
+      <c r="G47" t="n">
+        <v>56.08</v>
+      </c>
+      <c r="H47" t="n">
+        <v>46</v>
+      </c>
+      <c r="I47" t="n">
+        <v>67.8231</v>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>1:07.82</t>
+        </is>
+      </c>
+      <c r="K47" t="n">
+        <v>66.3425</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0.1596</v>
+      </c>
+      <c r="M47" t="n">
+        <v>1.3195</v>
+      </c>
+      <c r="N47" t="n">
+        <v>3099.5147</v>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>51:39.51</t>
+        </is>
+      </c>
+      <c r="P47" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>9,3,6,1,4,5,2,8,0,7</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>9:12;3:10;6:13;1:14;4:20;5:14;2:19;8:13;0:18;7:10</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>9:[17];3:[21];6:[17];1:[16];4:[18,19];5:[19];2:[17];8:[16];0:[18];7:[19]</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>c9:bw=12,experts=[17]; c3:bw=10,experts=[21]; c6:bw=13,experts=[17]; c1:bw=14,experts=[16]; c4:bw=20,experts=[18,19]; c5:bw=14,experts=[19]; c2:bw=19,experts=[17]; c8:bw=13,experts=[16]; c0:bw=18,experts=[18]; c7:bw=10,experts=[19]</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>4.6802,6.6878,8.6696,5.6516,8.9066,7.9275,4.8326,6.7851,6.1850,6.0166</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2026-09-25 05:29:23</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E48" t="n">
+        <v>1.634770673206543</v>
+      </c>
+      <c r="F48" t="n">
+        <v>55.69</v>
+      </c>
+      <c r="G48" t="n">
+        <v>56.08</v>
+      </c>
+      <c r="H48" t="n">
+        <v>46</v>
+      </c>
+      <c r="I48" t="n">
+        <v>68.68219999999999</v>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>1:08.68</t>
+        </is>
+      </c>
+      <c r="K48" t="n">
+        <v>67.2123</v>
+      </c>
+      <c r="L48" t="n">
+        <v>0.1515</v>
+      </c>
+      <c r="M48" t="n">
+        <v>1.3136</v>
+      </c>
+      <c r="N48" t="n">
+        <v>3168.2237</v>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>52:48.22</t>
+        </is>
+      </c>
+      <c r="P48" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>5,6,7,9,8,3,4,0,1,2</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>5:17;6:10;7:18;9:10;8:13;3:20;4:10;0:15;1:10;2:18</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>5:[20];6:[18];7:[20];9:[18];8:[17];3:[22,23];4:[20];0:[19];1:[17];2:[18]</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>c5:bw=17,experts=[20]; c6:bw=10,experts=[18]; c7:bw=18,experts=[20]; c9:bw=10,experts=[18]; c8:bw=13,experts=[17]; c3:bw=20,experts=[22,23]; c4:bw=10,experts=[20]; c0:bw=15,experts=[19]; c1:bw=10,experts=[17]; c2:bw=18,experts=[18]</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>7.9257,8.5288,6.1160,4.6312,7.0444,6.7606,9.4320,6.3058,5.5874,4.8802</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2026-09-25 05:30:31</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E49" t="n">
+        <v>1.626201380333891</v>
+      </c>
+      <c r="F49" t="n">
+        <v>55.85</v>
+      </c>
+      <c r="G49" t="n">
+        <v>56.08</v>
+      </c>
+      <c r="H49" t="n">
+        <v>46</v>
+      </c>
+      <c r="I49" t="n">
+        <v>67.8633</v>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>1:07.86</t>
+        </is>
+      </c>
+      <c r="K49" t="n">
+        <v>66.37739999999999</v>
+      </c>
+      <c r="L49" t="n">
+        <v>0.1532</v>
+      </c>
+      <c r="M49" t="n">
+        <v>1.3313</v>
+      </c>
+      <c r="N49" t="n">
+        <v>3236.1157</v>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>53:56.12</t>
+        </is>
+      </c>
+      <c r="P49" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>1,8,4,2,9,6,5,7,0,3</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>1:17;8:17;4:20;2:19;9:17;6:15;5:18;7:20;0:10;3:10</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>1:[18];8:[18];4:[21,22];2:[19];9:[19];6:[19];5:[21];7:[21,22];0:[20];3:[24]</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>c1:bw=17,experts=[18]; c8:bw=17,experts=[18]; c4:bw=20,experts=[21,22]; c2:bw=19,experts=[19]; c9:bw=17,experts=[19]; c6:bw=15,experts=[19]; c5:bw=18,experts=[21]; c7:bw=20,experts=[21,22]; c0:bw=10,experts=[20]; c3:bw=10,experts=[24]</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>5.6152,6.8960,8.8938,4.8775,4.5395,8.8484,8.1195,5.9791,6.0067,6.6017</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2026-09-25 05:31:40</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E50" t="n">
+        <v>1.624066871699154</v>
+      </c>
+      <c r="F50" t="n">
+        <v>56.34</v>
+      </c>
+      <c r="G50" t="n">
+        <v>56.34</v>
+      </c>
+      <c r="H50" t="n">
+        <v>49</v>
+      </c>
+      <c r="I50" t="n">
+        <v>68.7855</v>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>1:08.79</t>
+        </is>
+      </c>
+      <c r="K50" t="n">
+        <v>67.30929999999999</v>
+      </c>
+      <c r="L50" t="n">
+        <v>0.1516</v>
+      </c>
+      <c r="M50" t="n">
+        <v>1.3193</v>
+      </c>
+      <c r="N50" t="n">
+        <v>3304.9302</v>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>55:04.93</t>
+        </is>
+      </c>
+      <c r="P50" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>4,3,8,0,2,5,6,7,9,1</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>4:16;3:11;8:10;0:10;2:19;5:19;6:10;7:15;9:18;1:18</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>4:[23];3:[25];8:[19];0:[21];2:[20];5:[22];6:[20];7:[23];9:[20];1:[19]</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>c4:bw=16,experts=[23]; c3:bw=11,experts=[25]; c8:bw=10,experts=[19]; c0:bw=10,experts=[21]; c2:bw=19,experts=[20]; c5:bw=19,experts=[22]; c6:bw=10,experts=[20]; c7:bw=15,experts=[23]; c9:bw=18,experts=[20]; c1:bw=18,experts=[19]</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>8.9987,6.6903,7.1519,6.2614,5.0835,8.1499,8.6662,6.0736,4.6066,5.6270</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2026-09-25 05:32:48</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E51" t="n">
+        <v>1.615280838433308</v>
+      </c>
+      <c r="F51" t="n">
+        <v>56.59</v>
+      </c>
+      <c r="G51" t="n">
+        <v>56.59</v>
+      </c>
+      <c r="H51" t="n">
+        <v>50</v>
+      </c>
+      <c r="I51" t="n">
+        <v>68.1554</v>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>1:08.16</t>
+        </is>
+      </c>
+      <c r="K51" t="n">
+        <v>66.6383</v>
+      </c>
+      <c r="L51" t="n">
+        <v>0.1652</v>
+      </c>
+      <c r="M51" t="n">
+        <v>1.3503</v>
+      </c>
+      <c r="N51" t="n">
+        <v>3373.114</v>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>56:13.11</t>
+        </is>
+      </c>
+      <c r="P51" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>8,4,7,6,2,1,3,0,9,5</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>8:11;4:10;7:11;6:20;2:20;1:20;3:13;0:10;9:10;5:10</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>8:[20];4:[24];7:[24];6:[21,22];2:[21,22];1:[20,21];3:[26];0:[22];9:[21];5:[23]</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>c8:bw=11,experts=[20]; c4:bw=10,experts=[24]; c7:bw=11,experts=[24]; c6:bw=20,experts=[21,22]; c2:bw=20,experts=[21,22]; c1:bw=20,experts=[20,21]; c3:bw=13,experts=[26]; c0:bw=10,experts=[22]; c9:bw=10,experts=[21]; c5:bw=10,experts=[23]</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>6.9765,8.9066,5.9738,8.5211,4.8107,5.5107,6.6795,6.2235,4.7389,8.2969</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2026-09-25 05:33:57</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E52" t="n">
+        <v>1.609557187148025</v>
+      </c>
+      <c r="F52" t="n">
+        <v>56.42</v>
+      </c>
+      <c r="G52" t="n">
+        <v>56.59</v>
+      </c>
+      <c r="H52" t="n">
+        <v>50</v>
+      </c>
+      <c r="I52" t="n">
+        <v>68.4247</v>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>1:08.42</t>
+        </is>
+      </c>
+      <c r="K52" t="n">
+        <v>66.9739</v>
+      </c>
+      <c r="L52" t="n">
+        <v>0.158</v>
+      </c>
+      <c r="M52" t="n">
+        <v>1.2915</v>
+      </c>
+      <c r="N52" t="n">
+        <v>3441.5667</v>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>57:21.57</t>
+        </is>
+      </c>
+      <c r="P52" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>5,0,1,2,8,6,9,3,4,7</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>5:16;0:18;1:10;2:10;8:15;6:17;9:10;3:18;4:10;7:10</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>5:[24];0:[23];1:[22];2:[23];8:[21];6:[23];9:[22];3:[27];4:[25];7:[25]</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>c5:bw=16,experts=[24]; c0:bw=18,experts=[23]; c1:bw=10,experts=[22]; c2:bw=10,experts=[23]; c8:bw=15,experts=[21]; c6:bw=17,experts=[23]; c9:bw=10,experts=[22]; c3:bw=18,experts=[27]; c4:bw=10,experts=[25]; c7:bw=10,experts=[25]</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>8.2476,6.1453,5.7294,4.8854,6.8864,8.8167,4.6320,6.7576,8.9493,5.9240</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2026-09-25 05:35:05</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E53" t="n">
+        <v>1.598704762503726</v>
+      </c>
+      <c r="F53" t="n">
+        <v>56.6</v>
+      </c>
+      <c r="G53" t="n">
+        <v>56.6</v>
+      </c>
+      <c r="H53" t="n">
+        <v>52</v>
+      </c>
+      <c r="I53" t="n">
+        <v>68.4645</v>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>1:08.46</t>
+        </is>
+      </c>
+      <c r="K53" t="n">
+        <v>66.93170000000001</v>
+      </c>
+      <c r="L53" t="n">
+        <v>0.1685</v>
+      </c>
+      <c r="M53" t="n">
+        <v>1.3628</v>
+      </c>
+      <c r="N53" t="n">
+        <v>3510.0619</v>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>58:30.06</t>
+        </is>
+      </c>
+      <c r="P53" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>0,8,5,7,1,4,9,6,2,3</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>0:15;8:10;5:10;7:11;1:13;4:11;9:10;6:17;2:10;3:14</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>0:[24];8:[22];5:[25];7:[26];1:[23];4:[27];9:[23];6:[24];2:[24];3:[28]</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>c0:bw=15,experts=[24]; c8:bw=10,experts=[22]; c5:bw=10,experts=[25]; c7:bw=11,experts=[26]; c1:bw=13,experts=[23]; c4:bw=11,experts=[27]; c9:bw=10,experts=[23]; c6:bw=17,experts=[24]; c2:bw=10,experts=[24]; c3:bw=14,experts=[28]</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>6.0236,6.9157,8.1443,6.1473,5.6465,9.0703,4.6950,8.7163,4.9278,6.6450</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2026-09-25 05:36:08</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E54" t="n">
+        <v>1.595742992647334</v>
+      </c>
+      <c r="F54" t="n">
+        <v>57.11</v>
+      </c>
+      <c r="G54" t="n">
+        <v>57.11</v>
+      </c>
+      <c r="H54" t="n">
+        <v>53</v>
+      </c>
+      <c r="I54" t="n">
+        <v>62.3303</v>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>1:02.33</t>
+        </is>
+      </c>
+      <c r="K54" t="n">
+        <v>60.9992</v>
+      </c>
+      <c r="L54" t="n">
+        <v>0.1492</v>
+      </c>
+      <c r="M54" t="n">
+        <v>1.1806</v>
+      </c>
+      <c r="N54" t="n">
+        <v>3572.4205</v>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>59:32.42</t>
+        </is>
+      </c>
+      <c r="P54" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>8,4,5,1,3,9,6,7,0,2</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>8:10;4:10;5:15;1:20;3:16;9:20;6:12;7:15;0:13;2:17</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>8:[23];4:[28];5:[26];1:[24,25];3:[29];9:[24,25];6:[25];7:[27];0:[25];2:[25]</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>c8:bw=10,experts=[23]; c4:bw=10,experts=[28]; c5:bw=15,experts=[26]; c1:bw=20,experts=[24,25]; c3:bw=16,experts=[29]; c9:bw=20,experts=[24,25]; c6:bw=12,experts=[25]; c7:bw=15,experts=[27]; c0:bw=13,experts=[25]; c2:bw=17,experts=[25]</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>6.8360,8.4807,7.0501,4.8997,6.4182,4.3530,8.0364,5.3162,5.3265,4.2825</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2026-09-25 05:37:12</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E55" t="n">
+        <v>1.590098328009516</v>
+      </c>
+      <c r="F55" t="n">
+        <v>57.29</v>
+      </c>
+      <c r="G55" t="n">
+        <v>57.29</v>
+      </c>
+      <c r="H55" t="n">
+        <v>54</v>
+      </c>
+      <c r="I55" t="n">
+        <v>64.386</v>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>1:04.39</t>
+        </is>
+      </c>
+      <c r="K55" t="n">
+        <v>62.9066</v>
+      </c>
+      <c r="L55" t="n">
+        <v>0.1669</v>
+      </c>
+      <c r="M55" t="n">
+        <v>1.3111</v>
+      </c>
+      <c r="N55" t="n">
+        <v>3636.8311</v>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>1:00:36.83</t>
+        </is>
+      </c>
+      <c r="P55" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>2,1,8,7,3,0,6,5,9,4</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>2:10;1:18;8:18;7:20;3:10;0:12;6:18;5:10;9:17;4:11</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>2:[26];1:[26];8:[24];7:[28,29];3:[30];0:[26];6:[26];5:[27];9:[26];4:[29]</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>c2:bw=10,experts=[26]; c1:bw=18,experts=[26]; c8:bw=18,experts=[24]; c7:bw=20,experts=[28,29]; c3:bw=10,experts=[30]; c0:bw=12,experts=[26]; c6:bw=18,experts=[26]; c5:bw=10,experts=[27]; c9:bw=17,experts=[26]; c4:bw=11,experts=[29]</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>4.2820,4.8743,6.4469,5.7042,6.4558,5.9258,8.3161,7.7192,4.4559,8.7263</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2026-09-25 05:38:18</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E56" t="n">
+        <v>1.581632369625491</v>
+      </c>
+      <c r="F56" t="n">
+        <v>57.58</v>
+      </c>
+      <c r="G56" t="n">
+        <v>57.58</v>
+      </c>
+      <c r="H56" t="n">
+        <v>55</v>
+      </c>
+      <c r="I56" t="n">
+        <v>65.6628</v>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>1:05.66</t>
+        </is>
+      </c>
+      <c r="K56" t="n">
+        <v>64.23399999999999</v>
+      </c>
+      <c r="L56" t="n">
+        <v>0.1655</v>
+      </c>
+      <c r="M56" t="n">
+        <v>1.2619</v>
+      </c>
+      <c r="N56" t="n">
+        <v>3702.5238</v>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>1:01:42.52</t>
+        </is>
+      </c>
+      <c r="P56" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>7,2,4,3,8,5,1,6,0,9</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>7:18;2:14;4:10;3:17;8:10;5:18;1:20;6:14;0:10;9:20</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>7:[30];2:[27];4:[30];3:[31];8:[25];5:[28];1:[27,28];6:[27];0:[27];9:[27,28]</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>c7:bw=18,experts=[30]; c2:bw=14,experts=[27]; c4:bw=10,experts=[30]; c3:bw=17,experts=[31]; c8:bw=10,experts=[25]; c5:bw=18,experts=[28]; c1:bw=20,experts=[27,28]; c6:bw=14,experts=[27]; c0:bw=10,experts=[27]; c9:bw=20,experts=[27,28]</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>5.8608,4.6766,8.4720,6.4283,6.6254,7.8013,5.4655,8.5830,5.9295,4.3918</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2026-09-25 05:39:23</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E57" t="n">
+        <v>1.572898370378403</v>
+      </c>
+      <c r="F57" t="n">
+        <v>35.46</v>
+      </c>
+      <c r="G57" t="n">
+        <v>57.58</v>
+      </c>
+      <c r="H57" t="n">
+        <v>55</v>
+      </c>
+      <c r="I57" t="n">
+        <v>65.6292</v>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>1:05.63</t>
+        </is>
+      </c>
+      <c r="K57" t="n">
+        <v>64.0936</v>
+      </c>
+      <c r="L57" t="n">
+        <v>0.1609</v>
+      </c>
+      <c r="M57" t="n">
+        <v>1.3732</v>
+      </c>
+      <c r="N57" t="n">
+        <v>3768.1857</v>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>1:02:48.19</t>
+        </is>
+      </c>
+      <c r="P57" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>9,1,3,2,5,4,8,7,6,0</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>9:17;1:19;3:10;2:18;5:10;4:10;8:10;7:10;6:10;0:20</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>9:[29];1:[29];3:[4];2:[28];5:[29];4:[31];8:[26];7:[31];6:[28];0:[28,29]</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>c9:bw=17,experts=[29]; c1:bw=19,experts=[29]; c3:bw=10,experts=[4]; c2:bw=18,experts=[28]; c5:bw=10,experts=[29]; c4:bw=10,experts=[31]; c8:bw=10,experts=[26]; c7:bw=10,experts=[31]; c6:bw=10,experts=[28]; c0:bw=20,experts=[28,29]</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>4.3563,5.3565,6.3320,4.6530,7.7716,8.6641,6.8345,5.9098,8.3388,5.8768</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2026-09-25 05:40:34</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E58" t="n">
+        <v>1.593504329224067</v>
+      </c>
+      <c r="F58" t="n">
+        <v>42.64</v>
+      </c>
+      <c r="G58" t="n">
+        <v>57.58</v>
+      </c>
+      <c r="H58" t="n">
+        <v>55</v>
+      </c>
+      <c r="I58" t="n">
+        <v>70.4729</v>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>1:10.47</t>
+        </is>
+      </c>
+      <c r="K58" t="n">
+        <v>68.8933</v>
+      </c>
+      <c r="L58" t="n">
+        <v>0.1788</v>
+      </c>
+      <c r="M58" t="n">
+        <v>1.3992</v>
+      </c>
+      <c r="N58" t="n">
+        <v>3838.6893</v>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>1:03:58.69</t>
+        </is>
+      </c>
+      <c r="P58" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>3,8,6,1,7,0,5,4,2,9</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>3:20;8:14;6:16;1:16;7:20;0:20;5:15;4:14;2:11;9:10</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>3:[4,26];8:[27];6:[29];1:[30];7:[4,6];0:[30,31];5:[30];4:[6];2:[29];9:[30]</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>c3:bw=20,experts=[4,26]; c8:bw=14,experts=[27]; c6:bw=16,experts=[29]; c1:bw=16,experts=[30]; c7:bw=20,experts=[4,6]; c0:bw=20,experts=[30,31]; c5:bw=15,experts=[30]; c4:bw=14,experts=[6]; c2:bw=11,experts=[29]; c9:bw=10,experts=[30]</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>6.6348,7.0026,9.0777,5.8179,6.2805,6.4559,8.6139,9.0277,5.0917,4.8904</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2026-09-25 05:41:45</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E59" t="n">
+        <v>1.579181721475479</v>
+      </c>
+      <c r="F59" t="n">
+        <v>43.15</v>
+      </c>
+      <c r="G59" t="n">
+        <v>57.58</v>
+      </c>
+      <c r="H59" t="n">
+        <v>55</v>
+      </c>
+      <c r="I59" t="n">
+        <v>71.46250000000001</v>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>1:11.46</t>
+        </is>
+      </c>
+      <c r="K59" t="n">
+        <v>69.8823</v>
+      </c>
+      <c r="L59" t="n">
+        <v>0.1845</v>
+      </c>
+      <c r="M59" t="n">
+        <v>1.3906</v>
+      </c>
+      <c r="N59" t="n">
+        <v>3910.1812</v>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>1:05:10.18</t>
+        </is>
+      </c>
+      <c r="P59" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>7,2,9,6,5,1,8,4,3,0</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>7:10;2:10;9:19;6:18;5:12;1:10;8:13;4:13;3:20;0:16</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>7:[4];2:[30];9:[31];6:[30];5:[31];1:[31];8:[28];4:[26];3:[4,6];0:[6]</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>c7:bw=10,experts=[4]; c2:bw=10,experts=[30]; c9:bw=19,experts=[31]; c6:bw=18,experts=[30]; c5:bw=12,experts=[31]; c1:bw=10,experts=[31]; c8:bw=13,experts=[28]; c4:bw=13,experts=[26]; c3:bw=20,experts=[4,6]; c0:bw=16,experts=[6]</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>6.4094,5.1495,4.7923,9.1874,8.4874,5.8184,7.2150,9.3179,7.0776,6.4273</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2026-09-25 05:42:56</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E60" t="n">
+        <v>1.57555122500709</v>
+      </c>
+      <c r="F60" t="n">
+        <v>54.52</v>
+      </c>
+      <c r="G60" t="n">
+        <v>57.58</v>
+      </c>
+      <c r="H60" t="n">
+        <v>55</v>
+      </c>
+      <c r="I60" t="n">
+        <v>70.9385</v>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>1:10.94</t>
+        </is>
+      </c>
+      <c r="K60" t="n">
+        <v>69.35899999999999</v>
+      </c>
+      <c r="L60" t="n">
+        <v>0.1757</v>
+      </c>
+      <c r="M60" t="n">
+        <v>1.4024</v>
+      </c>
+      <c r="N60" t="n">
+        <v>3981.1517</v>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>1:06:21.15</t>
+        </is>
+      </c>
+      <c r="P60" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>2,8,9,6,1,4,7,5,0,3</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>2:12;8:19;9:10;6:10;1:20;4:10;7:10;5:11;0:17;3:12</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>2:[31];8:[29];9:[6];6:[31];1:[4,6];4:[4];7:[4];5:[4];0:[4];3:[4]</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>c2:bw=12,experts=[31]; c8:bw=19,experts=[29]; c9:bw=10,experts=[6]; c6:bw=10,experts=[31]; c1:bw=20,experts=[4,6]; c4:bw=10,experts=[4]; c7:bw=10,experts=[4]; c5:bw=11,experts=[4]; c0:bw=17,experts=[4]; c3:bw=12,experts=[4]</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>5.1023,7.2842,4.7505,8.9362,5.9037,9.2510,6.3175,8.5960,6.3020,6.9156</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2026-09-25 05:44:08</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E61" t="n">
+        <v>1.554830102000434</v>
+      </c>
+      <c r="F61" t="n">
+        <v>57.3</v>
+      </c>
+      <c r="G61" t="n">
+        <v>57.58</v>
+      </c>
+      <c r="H61" t="n">
+        <v>55</v>
+      </c>
+      <c r="I61" t="n">
+        <v>71.2676</v>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>1:11.27</t>
+        </is>
+      </c>
+      <c r="K61" t="n">
+        <v>69.6923</v>
+      </c>
+      <c r="L61" t="n">
+        <v>0.1745</v>
+      </c>
+      <c r="M61" t="n">
+        <v>1.3953</v>
+      </c>
+      <c r="N61" t="n">
+        <v>4052.4533</v>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>1:07:32.45</t>
+        </is>
+      </c>
+      <c r="P61" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>0,7,4,2,5,8,6,9,1,3</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>0:18;7:16;4:10;2:10;5:11;8:10;6:20;9:10;1:18;3:15</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>0:[4];7:[4];4:[4];2:[6];5:[4];8:[30];6:[4,6];9:[4];1:[4];3:[4]</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>c0:bw=18,experts=[4]; c7:bw=16,experts=[4]; c4:bw=10,experts=[4]; c2:bw=10,experts=[6]; c5:bw=11,experts=[4]; c8:bw=10,experts=[30]; c6:bw=20,experts=[4,6]; c9:bw=10,experts=[4]; c1:bw=18,experts=[4]; c3:bw=15,experts=[4]</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>6.3565,6.3122,9.2675,5.1083,8.4960,7.3283,9.0758,4.8664,5.8921,6.9893</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2026-09-25 05:45:19</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E62" t="n">
+        <v>1.548018707234974</v>
+      </c>
+      <c r="F62" t="n">
+        <v>58.61</v>
+      </c>
+      <c r="G62" t="n">
+        <v>58.61</v>
+      </c>
+      <c r="H62" t="n">
+        <v>61</v>
+      </c>
+      <c r="I62" t="n">
+        <v>71.8694</v>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>1:11.87</t>
+        </is>
+      </c>
+      <c r="K62" t="n">
+        <v>70.2804</v>
+      </c>
+      <c r="L62" t="n">
+        <v>0.1776</v>
+      </c>
+      <c r="M62" t="n">
+        <v>1.4098</v>
+      </c>
+      <c r="N62" t="n">
+        <v>4124.3511</v>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>1:08:44.35</t>
+        </is>
+      </c>
+      <c r="P62" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>5,6,2,9,1,3,8,4,7,0</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>5:16;6:12;2:10;9:13;1:11;3:14;8:18;4:13;7:14;0:20</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>5:[4];6:[4];2:[4];9:[4];1:[4];3:[4];8:[31];4:[4];7:[4];0:[4,6]</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>c5:bw=16,experts=[4]; c6:bw=12,experts=[4]; c2:bw=10,experts=[4]; c9:bw=13,experts=[4]; c1:bw=11,experts=[4]; c3:bw=14,experts=[4]; c8:bw=18,experts=[31]; c4:bw=13,experts=[4]; c7:bw=14,experts=[4]; c0:bw=20,experts=[4,6]</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>8.3034,9.0788,5.2047,4.9767,5.9716,7.0040,7.5706,9.4213,6.4334,6.3160</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2026-09-25 05:46:31</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E63" t="n">
+        <v>1.531824148576528</v>
+      </c>
+      <c r="F63" t="n">
+        <v>58.92</v>
+      </c>
+      <c r="G63" t="n">
+        <v>58.92</v>
+      </c>
+      <c r="H63" t="n">
+        <v>62</v>
+      </c>
+      <c r="I63" t="n">
+        <v>71.05540000000001</v>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>1:11.06</t>
+        </is>
+      </c>
+      <c r="K63" t="n">
+        <v>69.51819999999999</v>
+      </c>
+      <c r="L63" t="n">
+        <v>0.1672</v>
+      </c>
+      <c r="M63" t="n">
+        <v>1.3685</v>
+      </c>
+      <c r="N63" t="n">
+        <v>4195.4399</v>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>1:09:55.44</t>
+        </is>
+      </c>
+      <c r="P63" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>8,6,9,4,5,0,3,2,1,7</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>8:10;6:20;9:10;4:20;5:20;0:10;3:18;2:14;1:20;7:15</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>8:[6];6:[4,6];9:[4];4:[4,6];5:[4,26];0:[4];3:[4];2:[4];1:[4,6];7:[4]</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>c8:bw=10,experts=[6]; c6:bw=20,experts=[4,6]; c9:bw=10,experts=[4]; c4:bw=20,experts=[4,6]; c5:bw=20,experts=[4,26]; c0:bw=10,experts=[4]; c3:bw=18,experts=[4]; c2:bw=14,experts=[4]; c1:bw=20,experts=[4,6]; c7:bw=15,experts=[4]</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>7.3039,9.0179,4.7582,9.2488,8.5498,6.3608,7.0254,5.1743,5.8534,6.2258</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2026-09-25 05:47:42</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E64" t="n">
+        <v>1.520762646870572</v>
+      </c>
+      <c r="F64" t="n">
+        <v>59.03</v>
+      </c>
+      <c r="G64" t="n">
+        <v>59.03</v>
+      </c>
+      <c r="H64" t="n">
+        <v>63</v>
+      </c>
+      <c r="I64" t="n">
+        <v>71.5446</v>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>1:11.54</t>
+        </is>
+      </c>
+      <c r="K64" t="n">
+        <v>69.9799</v>
+      </c>
+      <c r="L64" t="n">
+        <v>0.1769</v>
+      </c>
+      <c r="M64" t="n">
+        <v>1.3863</v>
+      </c>
+      <c r="N64" t="n">
+        <v>4267.0175</v>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>1:11:07.02</t>
+        </is>
+      </c>
+      <c r="P64" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>5,9,6,3,8,1,7,0,2,4</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>5:10;9:10;6:11;3:17;8:11;1:17;7:20;0:14;2:10;4:17</t>
+        </is>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>5:[6];9:[4];6:[4];3:[4];8:[4];1:[4];7:[4,6];0:[4];2:[4];4:[4]</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>c5:bw=10,experts=[6]; c9:bw=10,experts=[4]; c6:bw=11,experts=[4]; c3:bw=17,experts=[4]; c8:bw=11,experts=[4]; c1:bw=17,experts=[4]; c7:bw=20,experts=[4,6]; c0:bw=14,experts=[4]; c2:bw=10,experts=[4]; c4:bw=17,experts=[4]</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>8.3321,4.8676,9.2913,7.0318,7.2428,5.9866,6.2810,6.4008,5.1490,9.3969</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2026-09-25 05:48:53</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E65" t="n">
+        <v>1.512141050284097</v>
+      </c>
+      <c r="F65" t="n">
+        <v>46.31</v>
+      </c>
+      <c r="G65" t="n">
+        <v>59.03</v>
+      </c>
+      <c r="H65" t="n">
+        <v>63</v>
+      </c>
+      <c r="I65" t="n">
+        <v>71.12739999999999</v>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>1:11.13</t>
+        </is>
+      </c>
+      <c r="K65" t="n">
+        <v>69.5608</v>
+      </c>
+      <c r="L65" t="n">
+        <v>0.1686</v>
+      </c>
+      <c r="M65" t="n">
+        <v>1.3963</v>
+      </c>
+      <c r="N65" t="n">
+        <v>4338.1785</v>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>1:12:18.18</t>
+        </is>
+      </c>
+      <c r="P65" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>6,4,5,3,7,0,8,9,2,1</t>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>6:17;4:13;5:10;3:13;7:11;0:11;8:18;9:20;2:19;1:10</t>
+        </is>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>6:[0];4:[0];5:[0];3:[0];7:[0];0:[0];8:[0];9:[0,4];2:[0];1:[0]</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>c6:bw=17,experts=[0]; c4:bw=13,experts=[0]; c5:bw=10,experts=[0]; c3:bw=13,experts=[0]; c7:bw=11,experts=[0]; c0:bw=11,experts=[0]; c8:bw=18,experts=[0]; c9:bw=20,experts=[0,4]; c2:bw=19,experts=[0]; c1:bw=10,experts=[0]</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>9.1562,9.2258,8.5313,6.9957,6.2312,6.3733,7.3211,4.7432,5.0990,5.8840</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2026-09-25 05:50:04</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E66" t="n">
+        <v>1.511447588516389</v>
+      </c>
+      <c r="F66" t="n">
+        <v>40.85</v>
+      </c>
+      <c r="G66" t="n">
+        <v>59.03</v>
+      </c>
+      <c r="H66" t="n">
+        <v>63</v>
+      </c>
+      <c r="I66" t="n">
+        <v>71.05840000000001</v>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>1:11.06</t>
+        </is>
+      </c>
+      <c r="K66" t="n">
+        <v>69.4811</v>
+      </c>
+      <c r="L66" t="n">
+        <v>0.1645</v>
+      </c>
+      <c r="M66" t="n">
+        <v>1.407</v>
+      </c>
+      <c r="N66" t="n">
+        <v>4409.2704</v>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>1:13:29.27</t>
+        </is>
+      </c>
+      <c r="P66" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>7,5,4,6,8,3,0,2,1,9</t>
+        </is>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>7:10;5:10;4:19;6:17;8:20;3:14;0:14;2:10;1:19;9:16</t>
+        </is>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>7:[1];5:[1];4:[1];6:[1];8:[1,4];3:[1];0:[1];2:[1];1:[1];9:[1]</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>c7:bw=10,experts=[1]; c5:bw=10,experts=[1]; c4:bw=19,experts=[1]; c6:bw=17,experts=[1]; c8:bw=20,experts=[1,4]; c3:bw=14,experts=[1]; c0:bw=14,experts=[1]; c2:bw=10,experts=[1]; c1:bw=19,experts=[1]; c9:bw=16,experts=[1]</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>6.3395,8.5611,9.1461,9.0641,7.1246,6.8313,6.3426,5.1258,6.0699,4.8761</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2026-09-25 05:51:16</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E67" t="n">
+        <v>1.529716594159664</v>
+      </c>
+      <c r="F67" t="n">
+        <v>44.4</v>
+      </c>
+      <c r="G67" t="n">
+        <v>59.03</v>
+      </c>
+      <c r="H67" t="n">
+        <v>63</v>
+      </c>
+      <c r="I67" t="n">
+        <v>71.1253</v>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>1:11.13</t>
+        </is>
+      </c>
+      <c r="K67" t="n">
+        <v>69.5446</v>
+      </c>
+      <c r="L67" t="n">
+        <v>0.1734</v>
+      </c>
+      <c r="M67" t="n">
+        <v>1.4057</v>
+      </c>
+      <c r="N67" t="n">
+        <v>4480.4249</v>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>1:14:40.42</t>
+        </is>
+      </c>
+      <c r="P67" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>2,5,1,8,9,6,4,0,3,7</t>
+        </is>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>2:14;5:10;1:18;8:10;9:10;6:10;4:14;0:13;3:20;7:17</t>
+        </is>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>2:[2];5:[2];1:[2];8:[2];9:[2];6:[2];4:[2];0:[2];3:[2,3];7:[2]</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>c2:bw=14,experts=[2]; c5:bw=10,experts=[2]; c1:bw=18,experts=[2]; c8:bw=10,experts=[2]; c9:bw=10,experts=[2]; c6:bw=10,experts=[2]; c4:bw=14,experts=[2]; c0:bw=13,experts=[2]; c3:bw=20,experts=[2,3]; c7:bw=17,experts=[2]</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>5.3000,8.5296,5.8864,7.0489,4.7217,8.9298,9.3300,6.4801,6.9754,6.3427</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2026-09-25 05:52:27</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E68" t="n">
+        <v>1.520119305669846</v>
+      </c>
+      <c r="F68" t="n">
+        <v>36.79</v>
+      </c>
+      <c r="G68" t="n">
+        <v>59.03</v>
+      </c>
+      <c r="H68" t="n">
+        <v>63</v>
+      </c>
+      <c r="I68" t="n">
+        <v>70.9323</v>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>1:10.93</t>
+        </is>
+      </c>
+      <c r="K68" t="n">
+        <v>69.36239999999999</v>
+      </c>
+      <c r="L68" t="n">
+        <v>0.1634</v>
+      </c>
+      <c r="M68" t="n">
+        <v>1.4051</v>
+      </c>
+      <c r="N68" t="n">
+        <v>4551.3928</v>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>1:15:51.39</t>
+        </is>
+      </c>
+      <c r="P68" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>4,5,1,3,6,0,2,9,7,8</t>
+        </is>
+      </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>4:17;5:16;1:12;3:10;6:18;0:11;2:14;9:20;7:20;8:10</t>
+        </is>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>4:[3];5:[3];1:[3];3:[5];6:[3];0:[3];2:[3];9:[3,5];7:[3,4];8:[3]</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>c4:bw=17,experts=[3]; c5:bw=16,experts=[3]; c1:bw=12,experts=[3]; c3:bw=10,experts=[5]; c6:bw=18,experts=[3]; c0:bw=11,experts=[3]; c2:bw=14,experts=[3]; c9:bw=20,experts=[3,5]; c7:bw=20,experts=[3,4]; c8:bw=10,experts=[3]</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>9.1185,8.3079,5.7307,7.0138,9.2254,6.5709,5.1713,4.7861,6.2425,7.1952</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2026-09-25 05:53:38</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E69" t="n">
+        <v>1.524913204578041</v>
+      </c>
+      <c r="F69" t="n">
+        <v>40.63</v>
+      </c>
+      <c r="G69" t="n">
+        <v>59.03</v>
+      </c>
+      <c r="H69" t="n">
+        <v>63</v>
+      </c>
+      <c r="I69" t="n">
+        <v>71.1105</v>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>1:11.11</t>
+        </is>
+      </c>
+      <c r="K69" t="n">
+        <v>69.5026</v>
+      </c>
+      <c r="L69" t="n">
+        <v>0.1785</v>
+      </c>
+      <c r="M69" t="n">
+        <v>1.4279</v>
+      </c>
+      <c r="N69" t="n">
+        <v>4622.5363</v>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>1:17:02.54</t>
+        </is>
+      </c>
+      <c r="P69" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>1,8,2,0,3,4,5,9,7,6</t>
+        </is>
+      </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>1:14;8:10;2:19;0:10;3:10;4:16;5:15;9:10;7:10;6:11</t>
+        </is>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>1:[5];8:[5];2:[5];0:[5];3:[7];4:[5];5:[5];9:[7];7:[5];6:[5]</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>c1:bw=14,experts=[5]; c8:bw=10,experts=[5]; c2:bw=19,experts=[5]; c0:bw=10,experts=[5]; c3:bw=10,experts=[7]; c4:bw=16,experts=[5]; c5:bw=15,experts=[5]; c9:bw=10,experts=[7]; c7:bw=10,experts=[5]; c6:bw=11,experts=[5]</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>5.7375,7.1053,5.2002,6.6651,7.1576,9.0770,8.4462,4.7983,6.2847,9.0306</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2026-09-25 05:54:49</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E70" t="n">
+        <v>1.516073796069921</v>
+      </c>
+      <c r="F70" t="n">
+        <v>40.19</v>
+      </c>
+      <c r="G70" t="n">
+        <v>59.03</v>
+      </c>
+      <c r="H70" t="n">
+        <v>63</v>
+      </c>
+      <c r="I70" t="n">
+        <v>71.60939999999999</v>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>1:11.61</t>
+        </is>
+      </c>
+      <c r="K70" t="n">
+        <v>69.9983</v>
+      </c>
+      <c r="L70" t="n">
+        <v>0.1962</v>
+      </c>
+      <c r="M70" t="n">
+        <v>1.4076</v>
+      </c>
+      <c r="N70" t="n">
+        <v>4694.1797</v>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>1:18:14.18</t>
+        </is>
+      </c>
+      <c r="P70" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>3,7,1,4,9,5,0,2,8,6</t>
+        </is>
+      </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>3:14;7:19;1:10;4:14;9:12;5:13;0:17;2:20;8:14;6:10</t>
+        </is>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>3:[8];7:[7];1:[7];4:[7];9:[8];5:[7];0:[7];2:[4,7];8:[7];6:[7]</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>c3:bw=14,experts=[8]; c7:bw=19,experts=[7]; c1:bw=10,experts=[7]; c4:bw=14,experts=[7]; c9:bw=12,experts=[8]; c5:bw=13,experts=[7]; c0:bw=17,experts=[7]; c2:bw=20,experts=[4,7]; c8:bw=14,experts=[7]; c6:bw=10,experts=[7]</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>7.1155,6.4660,5.9770,9.0276,4.7315,8.4413,6.3693,5.0899,7.4130,9.3671</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2026-09-25 05:56:01</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E71" t="n">
+        <v>1.506745509841385</v>
+      </c>
+      <c r="F71" t="n">
+        <v>43.72</v>
+      </c>
+      <c r="G71" t="n">
+        <v>59.03</v>
+      </c>
+      <c r="H71" t="n">
+        <v>63</v>
+      </c>
+      <c r="I71" t="n">
+        <v>71.2529</v>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>1:11.25</t>
+        </is>
+      </c>
+      <c r="K71" t="n">
+        <v>69.6799</v>
+      </c>
+      <c r="L71" t="n">
+        <v>0.1839</v>
+      </c>
+      <c r="M71" t="n">
+        <v>1.3878</v>
+      </c>
+      <c r="N71" t="n">
+        <v>4765.4669</v>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>1:19:25.47</t>
+        </is>
+      </c>
+      <c r="P71" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>1,9,7,3,0,6,2,4,5,8</t>
+        </is>
+      </c>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>1:10;9:10;7:10;3:11;0:10;6:10;2:18;4:19;5:10;8:16</t>
+        </is>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>1:[8];9:[9];7:[8];3:[9];0:[8];6:[8];2:[8];4:[8];5:[8];8:[8]</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>c1:bw=10,experts=[8]; c9:bw=10,experts=[9]; c7:bw=10,experts=[8]; c3:bw=11,experts=[9]; c0:bw=10,experts=[8]; c6:bw=10,experts=[8]; c2:bw=18,experts=[8]; c4:bw=19,experts=[8]; c5:bw=10,experts=[8]; c8:bw=16,experts=[8]</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>5.9319,4.7926,6.1119,6.8710,6.2355,9.1635,5.2758,9.3620,8.6046,7.3312</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2026-09-25 05:57:12</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E72" t="n">
+        <v>1.499721625574157</v>
+      </c>
+      <c r="F72" t="n">
+        <v>41.21</v>
+      </c>
+      <c r="G72" t="n">
+        <v>59.03</v>
+      </c>
+      <c r="H72" t="n">
+        <v>63</v>
+      </c>
+      <c r="I72" t="n">
+        <v>71.1635</v>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>1:11.16</t>
+        </is>
+      </c>
+      <c r="K72" t="n">
+        <v>69.57170000000001</v>
+      </c>
+      <c r="L72" t="n">
+        <v>0.1809</v>
+      </c>
+      <c r="M72" t="n">
+        <v>1.4048</v>
+      </c>
+      <c r="N72" t="n">
+        <v>4836.6639</v>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>1:20:36.66</t>
+        </is>
+      </c>
+      <c r="P72" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>4,0,1,9,7,5,3,6,8,2</t>
+        </is>
+      </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>4:14;0:10;1:17;9:13;7:10;5:11;3:20;6:17;8:13;2:20</t>
+        </is>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>4:[9];0:[9];1:[9];9:[10];7:[9];5:[9];3:[10,11];6:[9];8:[9];2:[4,9]</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>c4:bw=14,experts=[9]; c0:bw=10,experts=[9]; c1:bw=17,experts=[9]; c9:bw=13,experts=[10]; c7:bw=10,experts=[9]; c5:bw=11,experts=[9]; c3:bw=20,experts=[10,11]; c6:bw=17,experts=[9]; c8:bw=13,experts=[9]; c2:bw=20,experts=[4,9]</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>8.9992,6.2845,5.8001,4.8063,6.3354,8.4498,7.0357,9.1844,7.3708,5.3054</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2026-09-25 05:58:23</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E73" t="n">
+        <v>1.497995274520596</v>
+      </c>
+      <c r="F73" t="n">
+        <v>42.67</v>
+      </c>
+      <c r="G73" t="n">
+        <v>59.03</v>
+      </c>
+      <c r="H73" t="n">
+        <v>63</v>
+      </c>
+      <c r="I73" t="n">
+        <v>71.3372</v>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>1:11.34</t>
+        </is>
+      </c>
+      <c r="K73" t="n">
+        <v>69.6846</v>
+      </c>
+      <c r="L73" t="n">
+        <v>0.1871</v>
+      </c>
+      <c r="M73" t="n">
+        <v>1.4639</v>
+      </c>
+      <c r="N73" t="n">
+        <v>4908.0357</v>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>1:21:48.04</t>
+        </is>
+      </c>
+      <c r="P73" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>8,1,5,7,6,0,3,2,9,4</t>
+        </is>
+      </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>8:10;1:13;5:14;7:16;6:10;0:17;3:10;2:10;9:13;4:13</t>
+        </is>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>8:[10];1:[10];5:[10];7:[10];6:[10];0:[10];3:[12];2:[10];9:[11];4:[10]</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>c8:bw=10,experts=[10]; c1:bw=13,experts=[10]; c5:bw=14,experts=[10]; c7:bw=16,experts=[10]; c6:bw=10,experts=[10]; c0:bw=17,experts=[10]; c3:bw=10,experts=[12]; c2:bw=10,experts=[10]; c9:bw=13,experts=[11]; c4:bw=13,experts=[10]</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>7.1669,5.9819,8.6154,6.1736,9.0807,6.4542,6.9464,5.0776,4.7863,9.4016</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>2026-09-25 05:59:34</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E74" t="n">
+        <v>1.493550604438415</v>
+      </c>
+      <c r="F74" t="n">
+        <v>46.21</v>
+      </c>
+      <c r="G74" t="n">
+        <v>59.03</v>
+      </c>
+      <c r="H74" t="n">
+        <v>63</v>
+      </c>
+      <c r="I74" t="n">
+        <v>71.22920000000001</v>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>1:11.23</t>
+        </is>
+      </c>
+      <c r="K74" t="n">
+        <v>69.66370000000001</v>
+      </c>
+      <c r="L74" t="n">
+        <v>0.172</v>
+      </c>
+      <c r="M74" t="n">
+        <v>1.3867</v>
+      </c>
+      <c r="N74" t="n">
+        <v>4979.3005</v>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>1:22:59.30</t>
+        </is>
+      </c>
+      <c r="P74" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>2,8,3,1,5,9,0,7,6,4</t>
+        </is>
+      </c>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>2:16;8:10;3:13;1:20;5:10;9:17;0:10;7:12;6:10;4:14</t>
+        </is>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>2:[11];8:[11];3:[13];1:[4,11];5:[11];9:[12];0:[11];7:[11];6:[11];4:[11]</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>c2:bw=16,experts=[11]; c8:bw=10,experts=[11]; c3:bw=13,experts=[13]; c1:bw=20,experts=[4,11]; c5:bw=10,experts=[11]; c9:bw=17,experts=[12]; c0:bw=10,experts=[11]; c7:bw=12,experts=[11]; c6:bw=10,experts=[11]; c4:bw=14,experts=[11]</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>5.2899,7.1850,6.8870,5.9519,8.5720,4.8066,6.2556,6.3410,9.1716,9.2031</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>2026-09-25 06:00:46</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E75" t="n">
+        <v>1.483919792323543</v>
+      </c>
+      <c r="F75" t="n">
+        <v>49.52</v>
+      </c>
+      <c r="G75" t="n">
+        <v>59.03</v>
+      </c>
+      <c r="H75" t="n">
+        <v>63</v>
+      </c>
+      <c r="I75" t="n">
+        <v>71.5397</v>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>1:11.54</t>
+        </is>
+      </c>
+      <c r="K75" t="n">
+        <v>69.9569</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.1755</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1.4058</v>
+      </c>
+      <c r="N75" t="n">
+        <v>5050.8749</v>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>1:24:10.87</t>
+        </is>
+      </c>
+      <c r="P75" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>3,0,1,5,7,8,6,2,4,9</t>
+        </is>
+      </c>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>3:10;0:13;1:10;5:17;7:20;8:10;6:10;2:10;4:16;9:11</t>
+        </is>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>3:[14];0:[12];1:[12];5:[12];7:[12,13];8:[12];6:[12];2:[12];4:[12];9:[13]</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>c3:bw=10,experts=[14]; c0:bw=13,experts=[12]; c1:bw=10,experts=[12]; c5:bw=17,experts=[12]; c7:bw=20,experts=[12,13]; c8:bw=10,experts=[12]; c6:bw=10,experts=[12]; c2:bw=10,experts=[12]; c4:bw=16,experts=[12]; c9:bw=11,experts=[13]</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>7.0390,6.4300,5.9303,8.3480,6.3178,7.4559,9.2816,5.1613,9.1963,4.7967</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>2026-09-25 06:01:57</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E76" t="n">
+        <v>1.472023599429066</v>
+      </c>
+      <c r="F76" t="n">
+        <v>48.96</v>
+      </c>
+      <c r="G76" t="n">
+        <v>59.03</v>
+      </c>
+      <c r="H76" t="n">
+        <v>63</v>
+      </c>
+      <c r="I76" t="n">
+        <v>70.822</v>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>1:10.82</t>
+        </is>
+      </c>
+      <c r="K76" t="n">
+        <v>69.26179999999999</v>
+      </c>
+      <c r="L76" t="n">
+        <v>0.1697</v>
+      </c>
+      <c r="M76" t="n">
+        <v>1.3891</v>
+      </c>
+      <c r="N76" t="n">
+        <v>5121.7332</v>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>1:25:21.73</t>
+        </is>
+      </c>
+      <c r="P76" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>2,9,1,3,7,6,5,4,0,8</t>
+        </is>
+      </c>
+      <c r="R76" t="inlineStr">
+        <is>
+          <t>2:13;9:20;1:18;3:10;7:10;6:19;5:10;4:19;0:20;8:18</t>
+        </is>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>2:[13];9:[4,14];1:[13];3:[15];7:[14];6:[13];5:[13];4:[13];0:[13,14];8:[13]</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>c2:bw=13,experts=[13]; c9:bw=20,experts=[4,14]; c1:bw=18,experts=[13]; c3:bw=10,experts=[15]; c7:bw=10,experts=[14]; c6:bw=19,experts=[13]; c5:bw=10,experts=[13]; c4:bw=19,experts=[13]; c0:bw=20,experts=[13,14]; c8:bw=18,experts=[13]</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>5.1498,4.8398,5.9263,7.0195,6.2778,8.9385,8.3140,9.0506,6.3762,7.3692</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>2026-09-25 06:03:07</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E77" t="n">
+        <v>1.459450168893869</v>
+      </c>
+      <c r="F77" t="n">
+        <v>52.06</v>
+      </c>
+      <c r="G77" t="n">
+        <v>59.03</v>
+      </c>
+      <c r="H77" t="n">
+        <v>63</v>
+      </c>
+      <c r="I77" t="n">
+        <v>70.5287</v>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>1:10.53</t>
+        </is>
+      </c>
+      <c r="K77" t="n">
+        <v>69.05070000000001</v>
+      </c>
+      <c r="L77" t="n">
+        <v>0.173</v>
+      </c>
+      <c r="M77" t="n">
+        <v>1.2998</v>
+      </c>
+      <c r="N77" t="n">
+        <v>5192.2996</v>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>1:26:32.30</t>
+        </is>
+      </c>
+      <c r="P77" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>8,5,0,3,2,6,7,4,9,1</t>
+        </is>
+      </c>
+      <c r="R77" t="inlineStr">
+        <is>
+          <t>8:10;5:12;0:10;3:10;2:10;6:10;7:20;4:20;9:19;1:18</t>
+        </is>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>8:[14];5:[14];0:[15];3:[16];2:[14];6:[14];7:[15,16];4:[14,15];9:[15];1:[14]</t>
+        </is>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>c8:bw=10,experts=[14]; c5:bw=12,experts=[14]; c0:bw=10,experts=[15]; c3:bw=10,experts=[16]; c2:bw=10,experts=[14]; c6:bw=10,experts=[14]; c7:bw=20,experts=[15,16]; c4:bw=20,experts=[14,15]; c9:bw=19,experts=[15]; c1:bw=18,experts=[14]</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>7.2090,8.4069,6.2744,6.8239,5.0478,8.9377,6.3655,9.3867,4.8973,5.7015</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>2026-09-25 06:04:17</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E78" t="n">
+        <v>1.453793925278837</v>
+      </c>
+      <c r="F78" t="n">
+        <v>48.7</v>
+      </c>
+      <c r="G78" t="n">
+        <v>59.03</v>
+      </c>
+      <c r="H78" t="n">
+        <v>63</v>
+      </c>
+      <c r="I78" t="n">
+        <v>69.94499999999999</v>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>1:09.95</t>
+        </is>
+      </c>
+      <c r="K78" t="n">
+        <v>68.36839999999999</v>
+      </c>
+      <c r="L78" t="n">
+        <v>0.1653</v>
+      </c>
+      <c r="M78" t="n">
+        <v>1.4064</v>
+      </c>
+      <c r="N78" t="n">
+        <v>5262.2769</v>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>1:27:42.28</t>
+        </is>
+      </c>
+      <c r="P78" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>9,2,1,8,4,7,6,0,3,5</t>
+        </is>
+      </c>
+      <c r="R78" t="inlineStr">
+        <is>
+          <t>9:10;2:11;1:20;8:10;4:10;7:10;6:19;0:20;3:13;5:20</t>
+        </is>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>9:[16];2:[15];1:[4,15];8:[15];4:[16];7:[17];6:[15];0:[16,17];3:[17];5:[15,16]</t>
+        </is>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>c9:bw=10,experts=[16]; c2:bw=11,experts=[15]; c1:bw=20,experts=[4,15]; c8:bw=10,experts=[15]; c4:bw=10,experts=[16]; c7:bw=10,experts=[17]; c6:bw=19,experts=[15]; c0:bw=20,experts=[16,17]; c3:bw=13,experts=[17]; c5:bw=20,experts=[15,16]</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>4.5310,4.7571,5.4244,6.9832,9.0255,6.3932,9.2243,6.4791,7.0464,8.5043</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2026-09-25 06:05:29</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E79" t="n">
+        <v>1.461465356963424</v>
+      </c>
+      <c r="F79" t="n">
+        <v>50.75</v>
+      </c>
+      <c r="G79" t="n">
+        <v>59.03</v>
+      </c>
+      <c r="H79" t="n">
+        <v>63</v>
+      </c>
+      <c r="I79" t="n">
+        <v>71.7397</v>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>1:11.74</t>
+        </is>
+      </c>
+      <c r="K79" t="n">
+        <v>70.1523</v>
+      </c>
+      <c r="L79" t="n">
+        <v>0.1735</v>
+      </c>
+      <c r="M79" t="n">
+        <v>1.412</v>
+      </c>
+      <c r="N79" t="n">
+        <v>5334.0523</v>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>1:28:54.05</t>
+        </is>
+      </c>
+      <c r="P79" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>0,4,3,7,8,1,9,6,5,2</t>
+        </is>
+      </c>
+      <c r="R79" t="inlineStr">
+        <is>
+          <t>0:10;4:10;3:13;7:12;8:18;1:14;9:10;6:19;5:20;2:11</t>
+        </is>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>0:[18];4:[17];3:[18];7:[18];8:[16];1:[16];9:[17];6:[16];5:[17,18];2:[16]</t>
+        </is>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>c0:bw=10,experts=[18]; c4:bw=10,experts=[17]; c3:bw=13,experts=[18]; c7:bw=12,experts=[18]; c8:bw=18,experts=[16]; c1:bw=14,experts=[16]; c9:bw=10,experts=[17]; c6:bw=19,experts=[16]; c5:bw=20,experts=[17,18]; c2:bw=11,experts=[16]</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>6.3918,9.2711,7.0993,6.3099,7.4100,5.9976,4.8694,9.0234,8.4366,5.3432</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2026-09-25 06:06:41</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E80" t="n">
+        <v>1.4516552556257</v>
+      </c>
+      <c r="F80" t="n">
+        <v>52.53</v>
+      </c>
+      <c r="G80" t="n">
+        <v>59.03</v>
+      </c>
+      <c r="H80" t="n">
+        <v>63</v>
+      </c>
+      <c r="I80" t="n">
+        <v>71.5801</v>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>1:11.58</t>
+        </is>
+      </c>
+      <c r="K80" t="n">
+        <v>69.93340000000001</v>
+      </c>
+      <c r="L80" t="n">
+        <v>0.1903</v>
+      </c>
+      <c r="M80" t="n">
+        <v>1.4548</v>
+      </c>
+      <c r="N80" t="n">
+        <v>5405.6671</v>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>1:30:05.67</t>
+        </is>
+      </c>
+      <c r="P80" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>6,9,0,4,7,8,5,3,1,2</t>
+        </is>
+      </c>
+      <c r="R80" t="inlineStr">
+        <is>
+          <t>6:10;9:10;0:12;4:20;7:15;8:15;5:18;3:10;1:12;2:11</t>
+        </is>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>6:[17];9:[18];0:[19];4:[18,19];7:[19];8:[17];5:[19];3:[19];1:[17];2:[17]</t>
+        </is>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>c6:bw=10,experts=[17]; c9:bw=10,experts=[18]; c0:bw=12,experts=[19]; c4:bw=20,experts=[18,19]; c7:bw=15,experts=[19]; c8:bw=15,experts=[17]; c5:bw=18,experts=[19]; c3:bw=10,experts=[19]; c1:bw=12,experts=[17]; c2:bw=11,experts=[17]</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>9.0877,4.8679,6.5816,9.3429,6.2485,7.1548,8.5647,7.0141,5.8357,5.2355</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2026-09-25 06:07:52</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E81" t="n">
+        <v>1.448871488626545</v>
+      </c>
+      <c r="F81" t="n">
+        <v>53.48</v>
+      </c>
+      <c r="G81" t="n">
+        <v>59.03</v>
+      </c>
+      <c r="H81" t="n">
+        <v>63</v>
+      </c>
+      <c r="I81" t="n">
+        <v>71.0675</v>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>1:11.07</t>
+        </is>
+      </c>
+      <c r="K81" t="n">
+        <v>69.5003</v>
+      </c>
+      <c r="L81" t="n">
+        <v>0.1819</v>
+      </c>
+      <c r="M81" t="n">
+        <v>1.3838</v>
+      </c>
+      <c r="N81" t="n">
+        <v>5476.7724</v>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>1:31:16.77</t>
+        </is>
+      </c>
+      <c r="P81" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>5,9,7,1,3,4,2,0,6,8</t>
+        </is>
+      </c>
+      <c r="R81" t="inlineStr">
+        <is>
+          <t>5:20;9:18;7:16;1:10;3:10;4:19;2:15;0:16;6:13;8:17</t>
+        </is>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>5:[20,21];9:[19];7:[20];1:[18];3:[20];4:[20];2:[18];0:[20];6:[18];8:[18]</t>
+        </is>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>c5:bw=20,experts=[20,21]; c9:bw=18,experts=[19]; c7:bw=16,experts=[20]; c1:bw=10,experts=[18]; c3:bw=10,experts=[20]; c4:bw=19,experts=[20]; c2:bw=15,experts=[18]; c0:bw=16,experts=[20]; c6:bw=13,experts=[18]; c8:bw=17,experts=[18]</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>8.7014,4.7808,6.2015,5.7415,6.9622,9.0947,5.0510,6.3809,9.3386,7.2476</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>2026-09-25 06:09:03</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E82" t="n">
+        <v>1.44222377634588</v>
+      </c>
+      <c r="F82" t="n">
+        <v>53.9</v>
+      </c>
+      <c r="G82" t="n">
+        <v>59.03</v>
+      </c>
+      <c r="H82" t="n">
+        <v>63</v>
+      </c>
+      <c r="I82" t="n">
+        <v>71.51260000000001</v>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>1:11.51</t>
+        </is>
+      </c>
+      <c r="K82" t="n">
+        <v>69.8989</v>
+      </c>
+      <c r="L82" t="n">
+        <v>0.1863</v>
+      </c>
+      <c r="M82" t="n">
+        <v>1.4258</v>
+      </c>
+      <c r="N82" t="n">
+        <v>5548.3226</v>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>1:32:28.32</t>
+        </is>
+      </c>
+      <c r="P82" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>6,2,3,1,4,5,9,7,8,0</t>
+        </is>
+      </c>
+      <c r="R82" t="inlineStr">
+        <is>
+          <t>6:17;2:15;3:20;1:16;4:14;5:10;9:10;7:19;8:16;0:17</t>
+        </is>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>6:[19];2:[19];3:[21,22];1:[19];4:[21];5:[22];9:[20];7:[21];8:[19];0:[21]</t>
+        </is>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>c6:bw=17,experts=[19]; c2:bw=15,experts=[19]; c3:bw=20,experts=[21,22]; c1:bw=16,experts=[19]; c4:bw=14,experts=[21]; c5:bw=10,experts=[22]; c9:bw=10,experts=[20]; c7:bw=19,experts=[21]; c8:bw=16,experts=[19]; c0:bw=17,experts=[21]</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>8.9415,5.0847,6.9953,5.8856,9.3752,8.7145,4.8953,6.3294,7.2341,6.4434</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>2026-09-25 06:10:15</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E83" t="n">
+        <v>1.43477850707011</v>
+      </c>
+      <c r="F83" t="n">
+        <v>54.22</v>
+      </c>
+      <c r="G83" t="n">
+        <v>59.03</v>
+      </c>
+      <c r="H83" t="n">
+        <v>63</v>
+      </c>
+      <c r="I83" t="n">
+        <v>71.8258</v>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>1:11.83</t>
+        </is>
+      </c>
+      <c r="K83" t="n">
+        <v>70.233</v>
+      </c>
+      <c r="L83" t="n">
+        <v>0.1818</v>
+      </c>
+      <c r="M83" t="n">
+        <v>1.4096</v>
+      </c>
+      <c r="N83" t="n">
+        <v>5620.1863</v>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>1:33:40.19</t>
+        </is>
+      </c>
+      <c r="P83" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q83" t="inlineStr">
+        <is>
+          <t>1,0,6,8,7,3,2,9,5,4</t>
+        </is>
+      </c>
+      <c r="R83" t="inlineStr">
+        <is>
+          <t>1:20;0:10;6:12;8:19;7:13;3:13;2:10;9:19;5:13;4:10</t>
+        </is>
+      </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>1:[20,21];0:[22];6:[20];8:[20];7:[22];3:[23];2:[20];9:[21];5:[23];4:[22]</t>
+        </is>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>c1:bw=20,experts=[20,21]; c0:bw=10,experts=[22]; c6:bw=12,experts=[20]; c8:bw=19,experts=[20]; c7:bw=13,experts=[22]; c3:bw=13,experts=[23]; c2:bw=10,experts=[20]; c9:bw=19,experts=[21]; c5:bw=13,experts=[23]; c4:bw=10,experts=[22]</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>5.9217,6.3287,9.1661,7.4111,6.4147,7.0320,5.1454,4.9083,8.6097,9.2952</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>2026-09-25 06:11:26</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E84" t="n">
+        <v>1.432552242652267</v>
+      </c>
+      <c r="F84" t="n">
+        <v>49.07</v>
+      </c>
+      <c r="G84" t="n">
+        <v>59.03</v>
+      </c>
+      <c r="H84" t="n">
+        <v>63</v>
+      </c>
+      <c r="I84" t="n">
+        <v>70.9453</v>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>1:10.95</t>
+        </is>
+      </c>
+      <c r="K84" t="n">
+        <v>69.34229999999999</v>
+      </c>
+      <c r="L84" t="n">
+        <v>0.1834</v>
+      </c>
+      <c r="M84" t="n">
+        <v>1.4143</v>
+      </c>
+      <c r="N84" t="n">
+        <v>5691.1713</v>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>1:34:51.17</t>
+        </is>
+      </c>
+      <c r="P84" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q84" t="inlineStr">
+        <is>
+          <t>9,4,2,7,5,0,6,1,8,3</t>
+        </is>
+      </c>
+      <c r="R84" t="inlineStr">
+        <is>
+          <t>9:17;4:10;2:14;7:12;5:10;0:10;6:18;1:20;8:13;3:14</t>
+        </is>
+      </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>9:[22];4:[23];2:[21];7:[23];5:[24];0:[23];6:[21];1:[4,22];8:[21];3:[24]</t>
+        </is>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>c9:bw=17,experts=[22]; c4:bw=10,experts=[23]; c2:bw=14,experts=[21]; c7:bw=12,experts=[23]; c5:bw=10,experts=[24]; c0:bw=10,experts=[23]; c6:bw=18,experts=[21]; c1:bw=20,experts=[4,22]; c8:bw=13,experts=[21]; c3:bw=14,experts=[24]</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>4.7973,9.3913,5.1961,6.2700,8.5024,6.3766,8.9011,5.7201,7.1153,7.0721</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>2026-09-25 06:12:38</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E85" t="n">
+        <v>1.436525866830086</v>
+      </c>
+      <c r="F85" t="n">
+        <v>43.67</v>
+      </c>
+      <c r="G85" t="n">
+        <v>59.03</v>
+      </c>
+      <c r="H85" t="n">
+        <v>63</v>
+      </c>
+      <c r="I85" t="n">
+        <v>71.1849</v>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>1:11.18</t>
+        </is>
+      </c>
+      <c r="K85" t="n">
+        <v>69.57250000000001</v>
+      </c>
+      <c r="L85" t="n">
+        <v>0.1818</v>
+      </c>
+      <c r="M85" t="n">
+        <v>1.4246</v>
+      </c>
+      <c r="N85" t="n">
+        <v>5762.3955</v>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>1:36:02.40</t>
+        </is>
+      </c>
+      <c r="P85" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q85" t="inlineStr">
+        <is>
+          <t>8,3,1,6,9,2,7,5,4,0</t>
+        </is>
+      </c>
+      <c r="R85" t="inlineStr">
+        <is>
+          <t>8:20;3:11;1:19;6:10;9:10;2:12;7:16;5:10;4:10;0:10</t>
+        </is>
+      </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>8:[4,22];3:[25];1:[23];6:[22];9:[23];2:[22];7:[24];5:[25];4:[24];0:[24]</t>
+        </is>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>c8:bw=20,experts=[4,22]; c3:bw=11,experts=[25]; c1:bw=19,experts=[23]; c6:bw=10,experts=[22]; c9:bw=10,experts=[23]; c2:bw=12,experts=[22]; c7:bw=16,experts=[24]; c5:bw=10,experts=[25]; c4:bw=10,experts=[24]; c0:bw=10,experts=[24]</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>7.3782,6.8989,5.8246,8.9340,4.6883,5.0137,6.3356,8.6736,9.3145,6.5111</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>2026-09-25 06:13:49</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E86" t="n">
+        <v>1.439001887455507</v>
+      </c>
+      <c r="F86" t="n">
+        <v>52.87</v>
+      </c>
+      <c r="G86" t="n">
+        <v>59.03</v>
+      </c>
+      <c r="H86" t="n">
+        <v>63</v>
+      </c>
+      <c r="I86" t="n">
+        <v>71.5416</v>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>1:11.54</t>
+        </is>
+      </c>
+      <c r="K86" t="n">
+        <v>69.93899999999999</v>
+      </c>
+      <c r="L86" t="n">
+        <v>0.1738</v>
+      </c>
+      <c r="M86" t="n">
+        <v>1.4272</v>
+      </c>
+      <c r="N86" t="n">
+        <v>5833.9764</v>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>1:37:13.98</t>
+        </is>
+      </c>
+      <c r="P86" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t>0,2,8,6,1,4,9,3,5,7</t>
+        </is>
+      </c>
+      <c r="R86" t="inlineStr">
+        <is>
+          <t>0:13;2:15;8:20;6:14;1:19;4:14;9:19;3:17;5:10;7:10</t>
+        </is>
+      </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>0:[25];2:[23];8:[4,23];6:[23];1:[24];4:[25];9:[24];3:[27];5:[4];7:[25]</t>
+        </is>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>c0:bw=13,experts=[25]; c2:bw=15,experts=[23]; c8:bw=20,experts=[4,23]; c6:bw=14,experts=[23]; c1:bw=19,experts=[24]; c4:bw=14,experts=[25]; c9:bw=19,experts=[24]; c3:bw=17,experts=[27]; c5:bw=10,experts=[4]; c7:bw=10,experts=[25]</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>6.3932,5.1021,7.1997,9.1069,5.9522,9.4007,4.9004,7.0872,8.5206,6.2760</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>2026-09-25 06:14:59</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E87" t="n">
+        <v>1.423220499373873</v>
+      </c>
+      <c r="F87" t="n">
+        <v>54.99</v>
+      </c>
+      <c r="G87" t="n">
+        <v>59.03</v>
+      </c>
+      <c r="H87" t="n">
+        <v>63</v>
+      </c>
+      <c r="I87" t="n">
+        <v>70.1075</v>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>1:10.11</t>
+        </is>
+      </c>
+      <c r="K87" t="n">
+        <v>68.5506</v>
+      </c>
+      <c r="L87" t="n">
+        <v>0.1674</v>
+      </c>
+      <c r="M87" t="n">
+        <v>1.3881</v>
+      </c>
+      <c r="N87" t="n">
+        <v>5904.1241</v>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>1:38:24.12</t>
+        </is>
+      </c>
+      <c r="P87" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q87" t="inlineStr">
+        <is>
+          <t>5,8,2,6,0,4,7,3,1,9</t>
+        </is>
+      </c>
+      <c r="R87" t="inlineStr">
+        <is>
+          <t>5:16;8:10;2:10;6:18;0:10;4:10;7:15;3:10;1:20;9:14</t>
+        </is>
+      </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>5:[27];8:[24];2:[24];6:[24];0:[26];4:[27];7:[26];3:[28];1:[25,26];9:[25]</t>
+        </is>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>c5:bw=16,experts=[27]; c8:bw=10,experts=[24]; c2:bw=10,experts=[24]; c6:bw=18,experts=[24]; c0:bw=10,experts=[26]; c4:bw=10,experts=[27]; c7:bw=15,experts=[26]; c3:bw=10,experts=[28]; c1:bw=20,experts=[25,26]; c9:bw=14,experts=[25]</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>8.4992,7.3253,5.1841,9.2570,6.5818,9.0167,5.8455,6.4962,5.5381,4.8067</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>2026-09-25 06:16:10</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E88" t="n">
+        <v>1.416208947347392</v>
+      </c>
+      <c r="F88" t="n">
+        <v>57.09</v>
+      </c>
+      <c r="G88" t="n">
+        <v>59.03</v>
+      </c>
+      <c r="H88" t="n">
+        <v>63</v>
+      </c>
+      <c r="I88" t="n">
+        <v>70.68470000000001</v>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>1:10.68</t>
+        </is>
+      </c>
+      <c r="K88" t="n">
+        <v>69.0779</v>
+      </c>
+      <c r="L88" t="n">
+        <v>0.1685</v>
+      </c>
+      <c r="M88" t="n">
+        <v>1.4324</v>
+      </c>
+      <c r="N88" t="n">
+        <v>5974.8445</v>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>1:39:34.84</t>
+        </is>
+      </c>
+      <c r="P88" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q88" t="inlineStr">
+        <is>
+          <t>1,2,7,5,6,3,4,9,8,0</t>
+        </is>
+      </c>
+      <c r="R88" t="inlineStr">
+        <is>
+          <t>1:10;2:20;7:10;5:10;6:20;3:20;4:11;9:12;8:15;0:12</t>
+        </is>
+      </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>1:[27];2:[25,26];7:[27];5:[28];6:[25,26];3:[29,30];4:[28];9:[26];8:[25];0:[27]</t>
+        </is>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>c1:bw=10,experts=[27]; c2:bw=20,experts=[25,26]; c7:bw=10,experts=[27]; c5:bw=10,experts=[28]; c6:bw=20,experts=[25,26]; c3:bw=20,experts=[29,30]; c4:bw=11,experts=[28]; c9:bw=12,experts=[26]; c8:bw=15,experts=[25]; c0:bw=12,experts=[27]</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>5.6434,5.0984,6.3402,8.4776,8.9733,6.8513,9.2357,4.7977,7.1937,6.4668</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>2026-09-25 06:17:22</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E89" t="n">
+        <v>1.411052258829322</v>
+      </c>
+      <c r="F89" t="n">
+        <v>56.44</v>
+      </c>
+      <c r="G89" t="n">
+        <v>59.03</v>
+      </c>
+      <c r="H89" t="n">
+        <v>63</v>
+      </c>
+      <c r="I89" t="n">
+        <v>71.5132</v>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>1:11.51</t>
+        </is>
+      </c>
+      <c r="K89" t="n">
+        <v>69.9105</v>
+      </c>
+      <c r="L89" t="n">
+        <v>0.1722</v>
+      </c>
+      <c r="M89" t="n">
+        <v>1.4288</v>
+      </c>
+      <c r="N89" t="n">
+        <v>6046.3988</v>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>1:40:46.40</t>
+        </is>
+      </c>
+      <c r="P89" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q89" t="inlineStr">
+        <is>
+          <t>8,6,3,7,0,4,9,1,5,2</t>
+        </is>
+      </c>
+      <c r="R89" t="inlineStr">
+        <is>
+          <t>8:14;6:10;3:11;7:14;0:20;4:13;9:10;1:10;5:10;2:15</t>
+        </is>
+      </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>8:[26];6:[27];3:[31];7:[28];0:[28,29];4:[29];9:[27];1:[28];5:[29];2:[27]</t>
+        </is>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>c8:bw=14,experts=[26]; c6:bw=10,experts=[27]; c3:bw=11,experts=[31]; c7:bw=14,experts=[28]; c0:bw=20,experts=[28,29]; c4:bw=13,experts=[29]; c9:bw=10,experts=[27]; c1:bw=10,experts=[28]; c5:bw=10,experts=[29]; c2:bw=15,experts=[27]</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>7.2075,8.8607,6.7994,6.3060,6.4736,9.3753,5.0126,6.0968,8.5728,5.2059</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>2026-09-25 06:18:33</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E90" t="n">
+        <v>1.406609118467256</v>
+      </c>
+      <c r="F90" t="n">
+        <v>44.71</v>
+      </c>
+      <c r="G90" t="n">
+        <v>59.03</v>
+      </c>
+      <c r="H90" t="n">
+        <v>63</v>
+      </c>
+      <c r="I90" t="n">
+        <v>71.7131</v>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>1:11.71</t>
+        </is>
+      </c>
+      <c r="K90" t="n">
+        <v>70.13339999999999</v>
+      </c>
+      <c r="L90" t="n">
+        <v>0.1848</v>
+      </c>
+      <c r="M90" t="n">
+        <v>1.3935</v>
+      </c>
+      <c r="N90" t="n">
+        <v>6118.1517</v>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>1:41:58.15</t>
+        </is>
+      </c>
+      <c r="P90" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q90" t="inlineStr">
+        <is>
+          <t>3,8,2,9,7,5,0,6,4,1</t>
+        </is>
+      </c>
+      <c r="R90" t="inlineStr">
+        <is>
+          <t>3:10;8:20;2:15;9:20;7:10;5:15;0:10;6:11;4:10;1:14</t>
+        </is>
+      </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>3:[26];8:[4,27];2:[28];9:[28,29];7:[29];5:[30];0:[30];6:[28];4:[30];1:[29]</t>
+        </is>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>c3:bw=10,experts=[26]; c8:bw=20,experts=[4,27]; c2:bw=15,experts=[28]; c9:bw=20,experts=[28,29]; c7:bw=10,experts=[29]; c5:bw=15,experts=[30]; c0:bw=10,experts=[30]; c6:bw=11,experts=[28]; c4:bw=10,experts=[30]; c1:bw=14,experts=[29]</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>7.3399,7.4643,5.2491,4.9112,6.4138,8.7345,6.2647,8.6958,9.1464,5.9136</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>2026-09-25 06:19:47</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E91" t="n">
+        <v>1.411887004941951</v>
+      </c>
+      <c r="F91" t="n">
+        <v>44.7</v>
+      </c>
+      <c r="G91" t="n">
+        <v>59.03</v>
+      </c>
+      <c r="H91" t="n">
+        <v>63</v>
+      </c>
+      <c r="I91" t="n">
+        <v>73.4688</v>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>1:13.47</t>
+        </is>
+      </c>
+      <c r="K91" t="n">
+        <v>71.7749</v>
+      </c>
+      <c r="L91" t="n">
+        <v>0.2124</v>
+      </c>
+      <c r="M91" t="n">
+        <v>1.4799</v>
+      </c>
+      <c r="N91" t="n">
+        <v>6191.6604</v>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>1:43:11.66</t>
+        </is>
+      </c>
+      <c r="P91" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q91" t="inlineStr">
+        <is>
+          <t>7,1,3,9,0,6,2,5,8,4</t>
+        </is>
+      </c>
+      <c r="R91" t="inlineStr">
+        <is>
+          <t>7:20;1:10;3:12;9:20;0:20;6:10;2:10;5:10;8:17;4:12</t>
+        </is>
+      </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>7:[30,31];1:[30];3:[6];9:[30,31];0:[4,31];6:[29];2:[29];5:[31];8:[28];4:[31]</t>
+        </is>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>c7:bw=20,experts=[30,31]; c1:bw=10,experts=[30]; c3:bw=12,experts=[6]; c9:bw=20,experts=[30,31]; c0:bw=20,experts=[4,31]; c6:bw=10,experts=[29]; c2:bw=10,experts=[29]; c5:bw=10,experts=[31]; c8:bw=17,experts=[28]; c4:bw=12,experts=[31]</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>6.2067,6.1552,7.3445,5.0292,6.6240,9.2403,5.2035,8.6928,7.4522,9.8264</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>2026-09-25 06:21:00</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E92" t="n">
+        <v>1.418908999146448</v>
+      </c>
+      <c r="F92" t="n">
+        <v>59.7</v>
+      </c>
+      <c r="G92" t="n">
+        <v>59.7</v>
+      </c>
+      <c r="H92" t="n">
+        <v>91</v>
+      </c>
+      <c r="I92" t="n">
+        <v>72.8759</v>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>1:12.88</t>
+        </is>
+      </c>
+      <c r="K92" t="n">
+        <v>71.2718</v>
+      </c>
+      <c r="L92" t="n">
+        <v>0.1884</v>
+      </c>
+      <c r="M92" t="n">
+        <v>1.4143</v>
+      </c>
+      <c r="N92" t="n">
+        <v>6264.5791</v>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>1:44:24.58</t>
+        </is>
+      </c>
+      <c r="P92" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q92" t="inlineStr">
+        <is>
+          <t>1,9,5,7,3,4,0,6,2,8</t>
+        </is>
+      </c>
+      <c r="R92" t="inlineStr">
+        <is>
+          <t>1:17;9:12;5:17;7:17;3:13;4:18;0:10;6:10;2:10;8:10</t>
+        </is>
+      </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>1:[31];9:[6];5:[4];7:[4];3:[4];4:[26];0:[4];6:[30];2:[30];8:[29]</t>
+        </is>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>c1:bw=17,experts=[31]; c9:bw=12,experts=[6]; c5:bw=17,experts=[4]; c7:bw=17,experts=[4]; c3:bw=13,experts=[4]; c4:bw=18,experts=[26]; c0:bw=10,experts=[4]; c6:bw=10,experts=[30]; c2:bw=10,experts=[30]; c8:bw=10,experts=[29]</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>6.2210,4.9896,8.6382,6.3400,7.0057,9.3275,6.5754,9.3928,5.3597,7.4218</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>2026-09-25 06:22:12</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E93" t="n">
+        <v>1.386285917286085</v>
+      </c>
+      <c r="F93" t="n">
+        <v>63.33</v>
+      </c>
+      <c r="G93" t="n">
+        <v>63.33</v>
+      </c>
+      <c r="H93" t="n">
+        <v>92</v>
+      </c>
+      <c r="I93" t="n">
+        <v>71.75230000000001</v>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>1:11.75</t>
+        </is>
+      </c>
+      <c r="K93" t="n">
+        <v>70.1476</v>
+      </c>
+      <c r="L93" t="n">
+        <v>0.1832</v>
+      </c>
+      <c r="M93" t="n">
+        <v>1.4167</v>
+      </c>
+      <c r="N93" t="n">
+        <v>6336.3823</v>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>1:45:36.38</t>
+        </is>
+      </c>
+      <c r="P93" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q93" t="inlineStr">
+        <is>
+          <t>3,7,1,0,8,6,9,2,5,4</t>
+        </is>
+      </c>
+      <c r="R93" t="inlineStr">
+        <is>
+          <t>3:10;7:11;1:10;0:10;8:10;6:15;9:19;2:10;5:20;4:10</t>
+        </is>
+      </c>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>3:[4];7:[4];1:[4];0:[4];8:[30];6:[31];9:[4];2:[31];5:[4,6];4:[4]</t>
+        </is>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>c3:bw=10,experts=[4]; c7:bw=11,experts=[4]; c1:bw=10,experts=[4]; c0:bw=10,experts=[4]; c8:bw=10,experts=[30]; c6:bw=15,experts=[31]; c9:bw=19,experts=[4]; c2:bw=10,experts=[31]; c5:bw=20,experts=[4,6]; c4:bw=10,experts=[4]</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>6.9190,6.2330,5.7985,6.3407,7.2374,9.2009,4.9032,5.2273,8.8444,9.4432</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>2026-09-25 06:23:24</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E94" t="n">
+        <v>1.374090827486796</v>
+      </c>
+      <c r="F94" t="n">
+        <v>63.92</v>
+      </c>
+      <c r="G94" t="n">
+        <v>63.92</v>
+      </c>
+      <c r="H94" t="n">
+        <v>93</v>
+      </c>
+      <c r="I94" t="n">
+        <v>72.93129999999999</v>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>1:12.93</t>
+        </is>
+      </c>
+      <c r="K94" t="n">
+        <v>71.3207</v>
+      </c>
+      <c r="L94" t="n">
+        <v>0.1937</v>
+      </c>
+      <c r="M94" t="n">
+        <v>1.4153</v>
+      </c>
+      <c r="N94" t="n">
+        <v>6409.3662</v>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>1:46:49.37</t>
+        </is>
+      </c>
+      <c r="P94" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q94" t="inlineStr">
+        <is>
+          <t>1,3,7,9,6,8,5,4,0,2</t>
+        </is>
+      </c>
+      <c r="R94" t="inlineStr">
+        <is>
+          <t>1:16;3:10;7:10;9:19;6:10;8:10;5:10;4:11;0:10;2:17</t>
+        </is>
+      </c>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>1:[4];3:[4];7:[4];9:[4];6:[4];8:[31];5:[4];4:[4];0:[6];2:[6]</t>
+        </is>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>c1:bw=16,experts=[4]; c3:bw=10,experts=[4]; c7:bw=10,experts=[4]; c9:bw=19,experts=[4]; c6:bw=10,experts=[4]; c8:bw=10,experts=[31]; c5:bw=10,experts=[4]; c4:bw=11,experts=[4]; c0:bw=10,experts=[6]; c2:bw=17,experts=[6]</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>5.8908,7.0633,6.4683,4.9866,9.4415,7.4721,8.6278,9.4961,6.5648,5.3093</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>2026-09-25 06:24:38</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E95" t="n">
+        <v>1.372153281359924</v>
+      </c>
+      <c r="F95" t="n">
+        <v>63.79</v>
+      </c>
+      <c r="G95" t="n">
+        <v>63.92</v>
+      </c>
+      <c r="H95" t="n">
+        <v>93</v>
+      </c>
+      <c r="I95" t="n">
+        <v>73.17910000000001</v>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>1:13.18</t>
+        </is>
+      </c>
+      <c r="K95" t="n">
+        <v>71.5896</v>
+      </c>
+      <c r="L95" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="M95" t="n">
+        <v>1.408</v>
+      </c>
+      <c r="N95" t="n">
+        <v>6482.6013</v>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>1:48:02.60</t>
+        </is>
+      </c>
+      <c r="P95" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q95" t="inlineStr">
+        <is>
+          <t>7,2,5,4,6,9,1,8,0,3</t>
+        </is>
+      </c>
+      <c r="R95" t="inlineStr">
+        <is>
+          <t>7:15;2:20;5:14;4:10;6:10;9:17;1:20;8:10;0:18;3:11</t>
+        </is>
+      </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>7:[4];2:[4,6];5:[26];4:[6];6:[6];9:[4];1:[4,6];8:[6];0:[4];3:[4]</t>
+        </is>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>c7:bw=15,experts=[4]; c2:bw=20,experts=[4,6]; c5:bw=14,experts=[26]; c4:bw=10,experts=[6]; c6:bw=10,experts=[6]; c9:bw=17,experts=[4]; c1:bw=20,experts=[4,6]; c8:bw=10,experts=[6]; c0:bw=18,experts=[4]; c3:bw=11,experts=[4]</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>6.4460,5.2957,8.7577,9.4447,9.1685,4.9373,6.0802,7.5726,6.8784,7.0085</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>2026-09-25 06:25:50</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E96" t="n">
+        <v>1.364257121611401</v>
+      </c>
+      <c r="F96" t="n">
+        <v>64.98999999999999</v>
+      </c>
+      <c r="G96" t="n">
+        <v>64.98999999999999</v>
+      </c>
+      <c r="H96" t="n">
+        <v>95</v>
+      </c>
+      <c r="I96" t="n">
+        <v>71.864</v>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>1:11.86</t>
+        </is>
+      </c>
+      <c r="K96" t="n">
+        <v>70.2764</v>
+      </c>
+      <c r="L96" t="n">
+        <v>0.1714</v>
+      </c>
+      <c r="M96" t="n">
+        <v>1.4106</v>
+      </c>
+      <c r="N96" t="n">
+        <v>6554.52</v>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>1:49:14.52</t>
+        </is>
+      </c>
+      <c r="P96" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q96" t="inlineStr">
+        <is>
+          <t>7,9,4,6,0,3,1,8,2,5</t>
+        </is>
+      </c>
+      <c r="R96" t="inlineStr">
+        <is>
+          <t>7:20;9:14;4:10;6:13;0:12;3:14;1:10;8:20;2:10;5:10</t>
+        </is>
+      </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>7:[4,6];9:[4];4:[4];6:[4];0:[4];3:[4];1:[4];8:[4,6];2:[4];5:[4]</t>
+        </is>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>c7:bw=20,experts=[4,6]; c9:bw=14,experts=[4]; c4:bw=10,experts=[4]; c6:bw=13,experts=[4]; c0:bw=12,experts=[4]; c3:bw=14,experts=[4]; c1:bw=10,experts=[4]; c8:bw=20,experts=[4,6]; c2:bw=10,experts=[4]; c5:bw=10,experts=[4]</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>6.3867,4.8577,9.1581,9.1018,6.4726,7.1754,5.9817,7.2446,5.2515,8.6463</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>2026-09-25 06:27:02</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E97" t="n">
+        <v>1.357236838443513</v>
+      </c>
+      <c r="F97" t="n">
+        <v>60.22</v>
+      </c>
+      <c r="G97" t="n">
+        <v>64.98999999999999</v>
+      </c>
+      <c r="H97" t="n">
+        <v>95</v>
+      </c>
+      <c r="I97" t="n">
+        <v>72.31180000000001</v>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>1:12.31</t>
+        </is>
+      </c>
+      <c r="K97" t="n">
+        <v>70.7403</v>
+      </c>
+      <c r="L97" t="n">
+        <v>0.1671</v>
+      </c>
+      <c r="M97" t="n">
+        <v>1.4029</v>
+      </c>
+      <c r="N97" t="n">
+        <v>6626.8727</v>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>1:50:26.87</t>
+        </is>
+      </c>
+      <c r="P97" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q97" t="inlineStr">
+        <is>
+          <t>2,9,3,1,5,4,6,7,0,8</t>
+        </is>
+      </c>
+      <c r="R97" t="inlineStr">
+        <is>
+          <t>2:20;9:15;3:15;1:12;5:20;4:16;6:10;7:17;0:12;8:20</t>
+        </is>
+      </c>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>2:[0,4];9:[0];3:[0];1:[0];5:[0,4];4:[0];6:[0];7:[0];0:[0];8:[0,4]</t>
+        </is>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>c2:bw=20,experts=[0,4]; c9:bw=15,experts=[0]; c3:bw=15,experts=[0]; c1:bw=12,experts=[0]; c5:bw=20,experts=[0,4]; c4:bw=16,experts=[0]; c6:bw=10,experts=[0]; c7:bw=17,experts=[0]; c0:bw=12,experts=[0]; c8:bw=20,experts=[0,4]</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>5.1639,4.9362,7.1845,6.0780,8.8477,9.3384,9.1989,6.2886,6.4077,7.2963</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>2026-09-25 06:28:15</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E98" t="n">
+        <v>1.360793800329869</v>
+      </c>
+      <c r="F98" t="n">
+        <v>61.93</v>
+      </c>
+      <c r="G98" t="n">
+        <v>64.98999999999999</v>
+      </c>
+      <c r="H98" t="n">
+        <v>95</v>
+      </c>
+      <c r="I98" t="n">
+        <v>72.85850000000001</v>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>1:12.86</t>
+        </is>
+      </c>
+      <c r="K98" t="n">
+        <v>71.20950000000001</v>
+      </c>
+      <c r="L98" t="n">
+        <v>0.1912</v>
+      </c>
+      <c r="M98" t="n">
+        <v>1.4517</v>
+      </c>
+      <c r="N98" t="n">
+        <v>6699.7763</v>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>1:51:39.78</t>
+        </is>
+      </c>
+      <c r="P98" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q98" t="inlineStr">
+        <is>
+          <t>0,9,8,4,7,1,3,5,6,2</t>
+        </is>
+      </c>
+      <c r="R98" t="inlineStr">
+        <is>
+          <t>0:14;9:14;8:14;4:10;7:10;1:17;3:12;5:15;6:17;2:18</t>
+        </is>
+      </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>0:[1];9:[1];8:[1];4:[1];7:[1];1:[1];3:[1];5:[1];6:[1];2:[1]</t>
+        </is>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>c0:bw=14,experts=[1]; c9:bw=14,experts=[1]; c8:bw=14,experts=[1]; c4:bw=10,experts=[1]; c7:bw=10,experts=[1]; c1:bw=17,experts=[1]; c3:bw=12,experts=[1]; c5:bw=15,experts=[1]; c6:bw=17,experts=[1]; c2:bw=18,experts=[1]</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>6.3331,4.8258,7.3351,9.5658,6.6047,6.0461,7.2051,8.6758,9.3008,5.3172</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>2026-09-25 06:29:28</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E99" t="n">
+        <v>1.349304665753069</v>
+      </c>
+      <c r="F99" t="n">
+        <v>62.99</v>
+      </c>
+      <c r="G99" t="n">
+        <v>64.98999999999999</v>
+      </c>
+      <c r="H99" t="n">
+        <v>95</v>
+      </c>
+      <c r="I99" t="n">
+        <v>73.1585</v>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>1:13.16</t>
+        </is>
+      </c>
+      <c r="K99" t="n">
+        <v>71.5151</v>
+      </c>
+      <c r="L99" t="n">
+        <v>0.1967</v>
+      </c>
+      <c r="M99" t="n">
+        <v>1.4451</v>
+      </c>
+      <c r="N99" t="n">
+        <v>6772.9823</v>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>1:52:52.98</t>
+        </is>
+      </c>
+      <c r="P99" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q99" t="inlineStr">
+        <is>
+          <t>4,8,9,7,6,5,0,3,1,2</t>
+        </is>
+      </c>
+      <c r="R99" t="inlineStr">
+        <is>
+          <t>4:17;8:18;9:10;7:10;6:12;5:16;0:11;3:10;1:10;2:10</t>
+        </is>
+      </c>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>4:[2];8:[2];9:[2];7:[2];6:[2];5:[2];0:[2];3:[2];1:[2];2:[2]</t>
+        </is>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>c4:bw=17,experts=[2]; c8:bw=18,experts=[2]; c9:bw=10,experts=[2]; c7:bw=10,experts=[2]; c6:bw=12,experts=[2]; c5:bw=16,experts=[2]; c0:bw=11,experts=[2]; c3:bw=10,experts=[2]; c1:bw=10,experts=[2]; c2:bw=10,experts=[2]</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>9.3909,7.4836,5.0390,6.5850,9.3634,8.6300,6.5296,7.1626,6.0052,5.3257</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>2026-09-25 06:30:41</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E100" t="n">
+        <v>1.349023687338406</v>
+      </c>
+      <c r="F100" t="n">
+        <v>54.54</v>
+      </c>
+      <c r="G100" t="n">
+        <v>64.98999999999999</v>
+      </c>
+      <c r="H100" t="n">
+        <v>95</v>
+      </c>
+      <c r="I100" t="n">
+        <v>73.3085</v>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>1:13.31</t>
+        </is>
+      </c>
+      <c r="K100" t="n">
+        <v>71.67829999999999</v>
+      </c>
+      <c r="L100" t="n">
+        <v>0.1957</v>
+      </c>
+      <c r="M100" t="n">
+        <v>1.4295</v>
+      </c>
+      <c r="N100" t="n">
+        <v>6846.3367</v>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>1:54:06.34</t>
+        </is>
+      </c>
+      <c r="P100" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q100" t="inlineStr">
+        <is>
+          <t>8,5,7,1,3,9,4,0,2,6</t>
+        </is>
+      </c>
+      <c r="R100" t="inlineStr">
+        <is>
+          <t>8:11;5:16;7:15;1:20;3:13;9:10;4:10;0:13;2:10;6:12</t>
+        </is>
+      </c>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>8:[3];5:[3];7:[3];1:[3,4];3:[3];9:[3];4:[3];0:[3];2:[3];6:[3]</t>
+        </is>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>c8:bw=11,experts=[3]; c5:bw=16,experts=[3]; c7:bw=15,experts=[3]; c1:bw=20,experts=[3,4]; c3:bw=13,experts=[3]; c9:bw=10,experts=[3]; c4:bw=10,experts=[3]; c0:bw=13,experts=[3]; c2:bw=10,experts=[3]; c6:bw=12,experts=[3]</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>7.5031,8.8657,6.4422,6.1107,7.1503,4.8684,9.3748,6.5310,5.4698,9.3623</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>2026-09-25 06:31:53</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E101" t="n">
+        <v>1.350104591526015</v>
+      </c>
+      <c r="F101" t="n">
+        <v>56.8</v>
+      </c>
+      <c r="G101" t="n">
+        <v>64.98999999999999</v>
+      </c>
+      <c r="H101" t="n">
+        <v>95</v>
+      </c>
+      <c r="I101" t="n">
+        <v>71.7479</v>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>1:11.75</t>
+        </is>
+      </c>
+      <c r="K101" t="n">
+        <v>70.1781</v>
+      </c>
+      <c r="L101" t="n">
+        <v>0.1908</v>
+      </c>
+      <c r="M101" t="n">
+        <v>1.3775</v>
+      </c>
+      <c r="N101" t="n">
+        <v>6918.1273</v>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>1:55:18.13</t>
+        </is>
+      </c>
+      <c r="P101" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q101" t="inlineStr">
+        <is>
+          <t>2,8,9,5,6,1,4,7,3,0</t>
+        </is>
+      </c>
+      <c r="R101" t="inlineStr">
+        <is>
+          <t>2:10;8:15;9:18;5:10;6:15;1:10;4:20;7:10;3:14;0:20</t>
+        </is>
+      </c>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>2:[5];8:[5];9:[5];5:[5];6:[5];1:[5];4:[4,5];7:[5];3:[5];0:[4,5]</t>
+        </is>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>c2:bw=10,experts=[5]; c8:bw=15,experts=[5]; c9:bw=18,experts=[5]; c5:bw=10,experts=[5]; c6:bw=15,experts=[5]; c1:bw=10,experts=[5]; c4:bw=20,experts=[4,5]; c7:bw=10,experts=[5]; c3:bw=14,experts=[5]; c0:bw=20,experts=[4,5]</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>5.1607,7.3578,4.8494,8.4926,9.0636,5.9270,9.5141,6.4368,7.0027,6.3735</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
